--- a/upload/scm_po.xlsx
+++ b/upload/scm_po.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="70">
   <si>
     <t>Customer PO No.</t>
   </si>
@@ -117,6 +117,114 @@
   </si>
   <si>
     <t>Shipping Method</t>
+  </si>
+  <si>
+    <t>230769</t>
+  </si>
+  <si>
+    <t>3887ATE2-S</t>
+  </si>
+  <si>
+    <t>PEN</t>
+  </si>
+  <si>
+    <t>20240430</t>
+  </si>
+  <si>
+    <t>55NANO77SRA.AWF</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>2032.67</t>
+  </si>
+  <si>
+    <t>20240418</t>
+  </si>
+  <si>
+    <t>ESTILOS S.R.L.</t>
+  </si>
+  <si>
+    <t>55UR7300PSA.AWFQ</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>1783.66</t>
+  </si>
+  <si>
+    <t>65NANO77SRA.AWF</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>3070.17</t>
+  </si>
+  <si>
+    <t>65UR7300PSA.AWFQ</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>2323.17</t>
+  </si>
+  <si>
+    <t>No SKU: 2306300</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>2377.18</t>
+  </si>
+  <si>
+    <t>No SKU: 2306301</t>
+  </si>
+  <si>
+    <t>1319.12</t>
+  </si>
+  <si>
+    <t>75UR8750PSA.AWF</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>3033.18</t>
+  </si>
+  <si>
+    <t>No SKU: 2306303</t>
+  </si>
+  <si>
+    <t>2869.18</t>
+  </si>
+  <si>
+    <t>86UR8750PSA.AWF</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>6149.18</t>
+  </si>
+  <si>
+    <t>No SKU: 2306306</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3689.18</t>
+  </si>
+  <si>
+    <t>No SKU: 2306308</t>
+  </si>
+  <si>
+    <t>10659.18</t>
   </si>
 </sst>
 </file>
@@ -456,7 +564,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:AH1"/>
+  <dimension ref="A1:AH12"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:34">
@@ -562,6 +670,600 @@
       <c r="AH1" t="s">
         <v>33</v>
       </c>
+    </row>
+    <row r="2" spans="1:34">
+      <c r="A2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2"/>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
+      <c r="L2"/>
+      <c r="M2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N2"/>
+      <c r="O2"/>
+      <c r="P2"/>
+      <c r="Q2"/>
+      <c r="R2"/>
+      <c r="S2"/>
+      <c r="T2"/>
+      <c r="U2"/>
+      <c r="V2"/>
+      <c r="W2"/>
+      <c r="X2"/>
+      <c r="Y2"/>
+      <c r="Z2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA2"/>
+      <c r="AB2"/>
+      <c r="AC2"/>
+      <c r="AD2"/>
+      <c r="AE2"/>
+      <c r="AF2"/>
+      <c r="AG2"/>
+      <c r="AH2"/>
+    </row>
+    <row r="3" spans="1:34">
+      <c r="A3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H3"/>
+      <c r="I3"/>
+      <c r="J3"/>
+      <c r="K3"/>
+      <c r="L3"/>
+      <c r="M3" t="s">
+        <v>41</v>
+      </c>
+      <c r="N3"/>
+      <c r="O3"/>
+      <c r="P3"/>
+      <c r="Q3"/>
+      <c r="R3"/>
+      <c r="S3"/>
+      <c r="T3"/>
+      <c r="U3"/>
+      <c r="V3"/>
+      <c r="W3"/>
+      <c r="X3"/>
+      <c r="Y3"/>
+      <c r="Z3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA3"/>
+      <c r="AB3"/>
+      <c r="AC3"/>
+      <c r="AD3"/>
+      <c r="AE3"/>
+      <c r="AF3"/>
+      <c r="AG3"/>
+      <c r="AH3"/>
+    </row>
+    <row r="4" spans="1:34">
+      <c r="A4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H4"/>
+      <c r="I4"/>
+      <c r="J4"/>
+      <c r="K4"/>
+      <c r="L4"/>
+      <c r="M4" t="s">
+        <v>41</v>
+      </c>
+      <c r="N4"/>
+      <c r="O4"/>
+      <c r="P4"/>
+      <c r="Q4"/>
+      <c r="R4"/>
+      <c r="S4"/>
+      <c r="T4"/>
+      <c r="U4"/>
+      <c r="V4"/>
+      <c r="W4"/>
+      <c r="X4"/>
+      <c r="Y4"/>
+      <c r="Z4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA4"/>
+      <c r="AB4"/>
+      <c r="AC4"/>
+      <c r="AD4"/>
+      <c r="AE4"/>
+      <c r="AF4"/>
+      <c r="AG4"/>
+      <c r="AH4"/>
+    </row>
+    <row r="5" spans="1:34">
+      <c r="A5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G5" t="s">
+        <v>51</v>
+      </c>
+      <c r="H5"/>
+      <c r="I5"/>
+      <c r="J5"/>
+      <c r="K5"/>
+      <c r="L5"/>
+      <c r="M5" t="s">
+        <v>41</v>
+      </c>
+      <c r="N5"/>
+      <c r="O5"/>
+      <c r="P5"/>
+      <c r="Q5"/>
+      <c r="R5"/>
+      <c r="S5"/>
+      <c r="T5"/>
+      <c r="U5"/>
+      <c r="V5"/>
+      <c r="W5"/>
+      <c r="X5"/>
+      <c r="Y5"/>
+      <c r="Z5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA5"/>
+      <c r="AB5"/>
+      <c r="AC5"/>
+      <c r="AD5"/>
+      <c r="AE5"/>
+      <c r="AF5"/>
+      <c r="AG5"/>
+      <c r="AH5"/>
+    </row>
+    <row r="6" spans="1:34">
+      <c r="A6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F6" t="s">
+        <v>53</v>
+      </c>
+      <c r="G6" t="s">
+        <v>54</v>
+      </c>
+      <c r="H6"/>
+      <c r="I6"/>
+      <c r="J6"/>
+      <c r="K6"/>
+      <c r="L6"/>
+      <c r="M6" t="s">
+        <v>41</v>
+      </c>
+      <c r="N6"/>
+      <c r="O6"/>
+      <c r="P6"/>
+      <c r="Q6"/>
+      <c r="R6"/>
+      <c r="S6"/>
+      <c r="T6"/>
+      <c r="U6"/>
+      <c r="V6"/>
+      <c r="W6"/>
+      <c r="X6"/>
+      <c r="Y6"/>
+      <c r="Z6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA6"/>
+      <c r="AB6"/>
+      <c r="AC6"/>
+      <c r="AD6"/>
+      <c r="AE6"/>
+      <c r="AF6"/>
+      <c r="AG6"/>
+      <c r="AH6"/>
+    </row>
+    <row r="7" spans="1:34">
+      <c r="A7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G7" t="s">
+        <v>56</v>
+      </c>
+      <c r="H7"/>
+      <c r="I7"/>
+      <c r="J7"/>
+      <c r="K7"/>
+      <c r="L7"/>
+      <c r="M7" t="s">
+        <v>41</v>
+      </c>
+      <c r="N7"/>
+      <c r="O7"/>
+      <c r="P7"/>
+      <c r="Q7"/>
+      <c r="R7"/>
+      <c r="S7"/>
+      <c r="T7"/>
+      <c r="U7"/>
+      <c r="V7"/>
+      <c r="W7"/>
+      <c r="X7"/>
+      <c r="Y7"/>
+      <c r="Z7" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA7"/>
+      <c r="AB7"/>
+      <c r="AC7"/>
+      <c r="AD7"/>
+      <c r="AE7"/>
+      <c r="AF7"/>
+      <c r="AG7"/>
+      <c r="AH7"/>
+    </row>
+    <row r="8" spans="1:34">
+      <c r="A8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" t="s">
+        <v>57</v>
+      </c>
+      <c r="F8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H8"/>
+      <c r="I8"/>
+      <c r="J8"/>
+      <c r="K8"/>
+      <c r="L8"/>
+      <c r="M8" t="s">
+        <v>41</v>
+      </c>
+      <c r="N8"/>
+      <c r="O8"/>
+      <c r="P8"/>
+      <c r="Q8"/>
+      <c r="R8"/>
+      <c r="S8"/>
+      <c r="T8"/>
+      <c r="U8"/>
+      <c r="V8"/>
+      <c r="W8"/>
+      <c r="X8"/>
+      <c r="Y8"/>
+      <c r="Z8" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA8"/>
+      <c r="AB8"/>
+      <c r="AC8"/>
+      <c r="AD8"/>
+      <c r="AE8"/>
+      <c r="AF8"/>
+      <c r="AG8"/>
+      <c r="AH8"/>
+    </row>
+    <row r="9" spans="1:34">
+      <c r="A9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" t="s">
+        <v>60</v>
+      </c>
+      <c r="F9" t="s">
+        <v>58</v>
+      </c>
+      <c r="G9" t="s">
+        <v>61</v>
+      </c>
+      <c r="H9"/>
+      <c r="I9"/>
+      <c r="J9"/>
+      <c r="K9"/>
+      <c r="L9"/>
+      <c r="M9" t="s">
+        <v>41</v>
+      </c>
+      <c r="N9"/>
+      <c r="O9"/>
+      <c r="P9"/>
+      <c r="Q9"/>
+      <c r="R9"/>
+      <c r="S9"/>
+      <c r="T9"/>
+      <c r="U9"/>
+      <c r="V9"/>
+      <c r="W9"/>
+      <c r="X9"/>
+      <c r="Y9"/>
+      <c r="Z9" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA9"/>
+      <c r="AB9"/>
+      <c r="AC9"/>
+      <c r="AD9"/>
+      <c r="AE9"/>
+      <c r="AF9"/>
+      <c r="AG9"/>
+      <c r="AH9"/>
+    </row>
+    <row r="10" spans="1:34">
+      <c r="A10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" t="s">
+        <v>62</v>
+      </c>
+      <c r="F10" t="s">
+        <v>63</v>
+      </c>
+      <c r="G10" t="s">
+        <v>64</v>
+      </c>
+      <c r="H10"/>
+      <c r="I10"/>
+      <c r="J10"/>
+      <c r="K10"/>
+      <c r="L10"/>
+      <c r="M10" t="s">
+        <v>41</v>
+      </c>
+      <c r="N10"/>
+      <c r="O10"/>
+      <c r="P10"/>
+      <c r="Q10"/>
+      <c r="R10"/>
+      <c r="S10"/>
+      <c r="T10"/>
+      <c r="U10"/>
+      <c r="V10"/>
+      <c r="W10"/>
+      <c r="X10"/>
+      <c r="Y10"/>
+      <c r="Z10" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA10"/>
+      <c r="AB10"/>
+      <c r="AC10"/>
+      <c r="AD10"/>
+      <c r="AE10"/>
+      <c r="AF10"/>
+      <c r="AG10"/>
+      <c r="AH10"/>
+    </row>
+    <row r="11" spans="1:34">
+      <c r="A11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" t="s">
+        <v>65</v>
+      </c>
+      <c r="F11" t="s">
+        <v>66</v>
+      </c>
+      <c r="G11" t="s">
+        <v>67</v>
+      </c>
+      <c r="H11"/>
+      <c r="I11"/>
+      <c r="J11"/>
+      <c r="K11"/>
+      <c r="L11"/>
+      <c r="M11" t="s">
+        <v>41</v>
+      </c>
+      <c r="N11"/>
+      <c r="O11"/>
+      <c r="P11"/>
+      <c r="Q11"/>
+      <c r="R11"/>
+      <c r="S11"/>
+      <c r="T11"/>
+      <c r="U11"/>
+      <c r="V11"/>
+      <c r="W11"/>
+      <c r="X11"/>
+      <c r="Y11"/>
+      <c r="Z11" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA11"/>
+      <c r="AB11"/>
+      <c r="AC11"/>
+      <c r="AD11"/>
+      <c r="AE11"/>
+      <c r="AF11"/>
+      <c r="AG11"/>
+      <c r="AH11"/>
+    </row>
+    <row r="12" spans="1:34">
+      <c r="A12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F12" t="s">
+        <v>63</v>
+      </c>
+      <c r="G12" t="s">
+        <v>69</v>
+      </c>
+      <c r="H12"/>
+      <c r="I12"/>
+      <c r="J12"/>
+      <c r="K12"/>
+      <c r="L12"/>
+      <c r="M12" t="s">
+        <v>41</v>
+      </c>
+      <c r="N12"/>
+      <c r="O12"/>
+      <c r="P12"/>
+      <c r="Q12"/>
+      <c r="R12"/>
+      <c r="S12"/>
+      <c r="T12"/>
+      <c r="U12"/>
+      <c r="V12"/>
+      <c r="W12"/>
+      <c r="X12"/>
+      <c r="Y12"/>
+      <c r="Z12" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA12"/>
+      <c r="AB12"/>
+      <c r="AC12"/>
+      <c r="AD12"/>
+      <c r="AE12"/>
+      <c r="AF12"/>
+      <c r="AG12"/>
+      <c r="AH12"/>
     </row>
   </sheetData>
   <printOptions gridLines="false" gridLinesSet="true"/>
